--- a/data/availability/projects/hyde-park-developments/one-hyde-park-new-cairo.xlsx
+++ b/data/availability/projects/hyde-park-developments/one-hyde-park-new-cairo.xlsx
@@ -587,7 +587,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -637,7 +637,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1495,7 +1495,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1739,7 +1739,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1800,7 +1800,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1983,7 +1983,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
